--- a/就業金卡/20260228有效就業金卡國籍和領域分統計報表.xlsx
+++ b/就業金卡/20260228有效就業金卡國籍和領域分統計報表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrtbh\實驗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29FDD55-10B4-472C-A4AC-8C04A5171C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0099E5EF-CF8E-480B-A3FC-79D8EA84A978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{09D9F200-233C-244C-8558-CFFC2AD0F08A}"/>
   </bookViews>
@@ -63,10 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>文化藝術</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>教育</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -242,9 +238,6 @@
     <t>南非</t>
   </si>
   <si>
-    <t>南韓</t>
-  </si>
-  <si>
     <t>哈薩克</t>
   </si>
   <si>
@@ -429,6 +422,14 @@
   </si>
   <si>
     <t>運動</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韓國</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文化、藝術</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -852,22 +853,22 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -882,7 +883,7 @@
         <v>2</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -893,7 +894,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2">
         <v>4</v>
@@ -934,7 +935,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2">
         <v>13</v>
@@ -975,7 +976,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
@@ -1016,7 +1017,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
@@ -1057,7 +1058,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2">
         <v>7</v>
@@ -1098,7 +1099,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2">
         <v>0</v>
@@ -1139,7 +1140,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
@@ -1180,7 +1181,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2">
         <v>17</v>
@@ -1221,7 +1222,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2">
         <v>36</v>
@@ -1262,7 +1263,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2">
         <v>11</v>
@@ -1303,7 +1304,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2">
         <v>0</v>
@@ -1344,7 +1345,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2">
         <v>11</v>
@@ -1385,7 +1386,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2">
         <v>61</v>
@@ -1426,7 +1427,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -1467,7 +1468,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -1508,7 +1509,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2">
         <v>1</v>
@@ -1549,7 +1550,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -1590,7 +1591,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
@@ -1631,7 +1632,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2">
         <v>1</v>
@@ -1672,7 +1673,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="2">
         <v>0</v>
@@ -1713,7 +1714,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" s="2">
         <v>1</v>
@@ -1754,7 +1755,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="2">
         <v>0</v>
@@ -1795,7 +1796,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
@@ -1836,7 +1837,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2">
         <v>9</v>
@@ -1877,7 +1878,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2">
         <v>0</v>
@@ -1918,7 +1919,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27" s="2">
         <v>1</v>
@@ -1959,7 +1960,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="2">
         <v>14</v>
@@ -2000,7 +2001,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="2">
         <v>169</v>
@@ -2041,7 +2042,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2">
         <v>0</v>
@@ -2082,7 +2083,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2">
         <v>0</v>
@@ -2123,7 +2124,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="2">
         <v>3</v>
@@ -2164,7 +2165,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" s="2">
         <v>11</v>
@@ -2205,7 +2206,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34" s="2">
         <v>0</v>
@@ -2246,7 +2247,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" s="2">
         <v>2</v>
@@ -2287,7 +2288,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" s="2">
         <v>0</v>
@@ -2328,7 +2329,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="2">
         <v>0</v>
@@ -2369,7 +2370,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B38" s="2">
         <v>1</v>
@@ -2410,7 +2411,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B39" s="2">
         <v>2</v>
@@ -2451,7 +2452,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B40" s="2">
         <v>0</v>
@@ -2492,7 +2493,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" s="2">
         <v>0</v>
@@ -2533,7 +2534,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B42" s="2">
         <v>0</v>
@@ -2574,7 +2575,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" s="2">
         <v>0</v>
@@ -2615,7 +2616,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" s="2">
         <v>3</v>
@@ -2656,7 +2657,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B45" s="2">
         <v>7</v>
@@ -2697,7 +2698,7 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B46" s="2">
         <v>48</v>
@@ -2738,7 +2739,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B47" s="2">
         <v>0</v>
@@ -2779,7 +2780,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B48" s="2">
         <v>5</v>
@@ -2820,7 +2821,7 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B49" s="2">
         <v>0</v>
@@ -2861,7 +2862,7 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B50" s="2">
         <v>0</v>
@@ -2902,7 +2903,7 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B51" s="2">
         <v>1</v>
@@ -2943,7 +2944,7 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B52" s="2">
         <v>24</v>
@@ -2984,7 +2985,7 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B53" s="2">
         <v>1</v>
@@ -3025,7 +3026,7 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="B54" s="2">
         <v>34</v>
@@ -3066,7 +3067,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B55" s="2">
         <v>4</v>
@@ -3107,7 +3108,7 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B56" s="2">
         <v>0</v>
@@ -3148,7 +3149,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B57" s="2">
         <v>0</v>
@@ -3189,7 +3190,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B58" s="2">
         <v>1</v>
@@ -3230,7 +3231,7 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B59" s="2">
         <v>445</v>
@@ -3271,7 +3272,7 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B60" s="2">
         <v>67</v>
@@ -3312,7 +3313,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B61" s="2">
         <v>79</v>
@@ -3353,7 +3354,7 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B62" s="2">
         <v>0</v>
@@ -3394,7 +3395,7 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B63" s="2">
         <v>1</v>
@@ -3435,7 +3436,7 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B64" s="2">
         <v>2</v>
@@ -3476,7 +3477,7 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B65" s="2">
         <v>3</v>
@@ -3517,7 +3518,7 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B66" s="2">
         <v>1</v>
@@ -3558,7 +3559,7 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B67" s="2">
         <v>0</v>
@@ -3599,7 +3600,7 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B68" s="2">
         <v>3</v>
@@ -3640,7 +3641,7 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B69" s="2">
         <v>0</v>
@@ -3681,7 +3682,7 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B70" s="2">
         <v>6</v>
@@ -3722,7 +3723,7 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B71" s="2">
         <v>0</v>
@@ -3763,7 +3764,7 @@
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B72" s="2">
         <v>0</v>
@@ -3804,7 +3805,7 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B73" s="2">
         <v>0</v>
@@ -3845,7 +3846,7 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B74" s="2">
         <v>4</v>
@@ -3886,7 +3887,7 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B75" s="2">
         <v>67</v>
@@ -3927,7 +3928,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B76" s="2">
         <v>0</v>
@@ -3968,7 +3969,7 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B77" s="2">
         <v>1</v>
@@ -4009,7 +4010,7 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B78" s="2">
         <v>0</v>
@@ -4050,7 +4051,7 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B79" s="2">
         <v>16</v>
@@ -4091,7 +4092,7 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B80" s="2">
         <v>0</v>
@@ -4132,7 +4133,7 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B81" s="2">
         <v>0</v>
@@ -4173,7 +4174,7 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B82" s="2">
         <v>0</v>
@@ -4214,7 +4215,7 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B83" s="2">
         <v>1</v>
@@ -4255,7 +4256,7 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B84" s="2">
         <v>0</v>
@@ -4296,7 +4297,7 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B85" s="2">
         <v>0</v>
@@ -4337,7 +4338,7 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B86" s="2">
         <v>16</v>
@@ -4378,7 +4379,7 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B87" s="2">
         <v>22</v>
@@ -4419,7 +4420,7 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B88" s="2">
         <v>0</v>
@@ -4460,7 +4461,7 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B89" s="2">
         <v>4</v>
@@ -4501,7 +4502,7 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B90" s="2">
         <v>1</v>
@@ -4542,7 +4543,7 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B91" s="2">
         <v>4</v>
@@ -4583,7 +4584,7 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B92" s="2">
         <v>77</v>
@@ -4624,7 +4625,7 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B93" s="2">
         <v>7</v>
@@ -4665,7 +4666,7 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B94" s="2">
         <v>9</v>
@@ -4706,7 +4707,7 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B95" s="2">
         <v>0</v>
@@ -4747,7 +4748,7 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B96" s="2">
         <v>12</v>
@@ -4788,7 +4789,7 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B97" s="2">
         <v>1</v>
@@ -4829,7 +4830,7 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B98" s="2">
         <v>0</v>
@@ -4870,7 +4871,7 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B99" s="2">
         <v>1</v>
@@ -4911,7 +4912,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B100" s="2">
         <v>0</v>
@@ -4952,7 +4953,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B101" s="2">
         <v>4</v>
@@ -4993,7 +4994,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B102" s="2">
         <v>1</v>
@@ -5034,7 +5035,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B103" s="2">
         <v>42</v>
@@ -5075,7 +5076,7 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B104" s="2">
         <v>0</v>
@@ -5116,7 +5117,7 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B105" s="2">
         <v>0</v>
@@ -5157,7 +5158,7 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B106" s="2">
         <v>1</v>
@@ -5198,7 +5199,7 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B107" s="2">
         <v>6</v>
@@ -5239,7 +5240,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B108" s="2">
         <v>0</v>
@@ -5280,7 +5281,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B109" s="2">
         <v>2</v>
@@ -5321,7 +5322,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B110" s="2">
         <v>25</v>
@@ -5362,7 +5363,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B111" s="2">
         <v>1</v>
@@ -5403,7 +5404,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B112" s="2">
         <v>0</v>
@@ -5444,7 +5445,7 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B113" s="2">
         <v>5</v>
@@ -5485,7 +5486,7 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B114" s="2">
         <v>0</v>
@@ -5526,7 +5527,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B115" s="3">
         <v>1443</v>
@@ -5568,6 +5569,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>